--- a/artfynd/A 932-2024 artfynd.xlsx
+++ b/artfynd/A 932-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 932-2024 artfynd.xlsx
+++ b/artfynd/A 932-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113261792</v>
       </c>
       <c r="B2" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,16 +787,11 @@
         <v>114463762</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
